--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431E0A84-580E-45F0-8891-6E4C66C1823B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A37221-1DE8-48A6-8E3E-E4F74DA896EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>区域</t>
   </si>
@@ -52,6 +52,36 @@
     <t>美股</t>
   </si>
   <si>
+    <t>DELL US</t>
+  </si>
+  <si>
+    <t>戴尔科技</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>HPE US</t>
+  </si>
+  <si>
+    <t>慧与科技</t>
+  </si>
+  <si>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>NBIS US</t>
+  </si>
+  <si>
+    <t>Nebius</t>
+  </si>
+  <si>
+    <t>AI云</t>
+  </si>
+  <si>
     <t>SNOW US</t>
   </si>
   <si>
@@ -61,7 +91,10 @@
     <t>Software - Application</t>
   </si>
   <si>
-    <t>欧式敲入</t>
+    <t>AAOI US</t>
+  </si>
+  <si>
+    <t>Applied Optoelectronics</t>
   </si>
   <si>
     <t>NET US</t>
@@ -82,106 +115,76 @@
     <t>AI光通信</t>
   </si>
   <si>
-    <t>AXTI US</t>
-  </si>
-  <si>
-    <t>AXT Inc</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>PLTR US</t>
-  </si>
-  <si>
-    <t>Palantir</t>
-  </si>
-  <si>
-    <t>AI软件</t>
-  </si>
-  <si>
-    <t>AAOI US</t>
-  </si>
-  <si>
-    <t>Applied Optoelectronics</t>
-  </si>
-  <si>
-    <t>Communication Equipment</t>
-  </si>
-  <si>
-    <t>FCX US</t>
-  </si>
-  <si>
-    <t>麦克莫兰铜金</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>PH US</t>
-  </si>
-  <si>
-    <t>派克汉尼汾</t>
+    <t>VLO US</t>
+  </si>
+  <si>
+    <t>瓦莱罗能源</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>ANET US</t>
+  </si>
+  <si>
+    <t>Arista</t>
+  </si>
+  <si>
+    <t>AI网络</t>
+  </si>
+  <si>
+    <t>SNDK US</t>
+  </si>
+  <si>
+    <t>闪迪</t>
+  </si>
+  <si>
+    <t>WDAY US</t>
+  </si>
+  <si>
+    <t>Workday</t>
+  </si>
+  <si>
+    <t>CRWV US</t>
+  </si>
+  <si>
+    <t>CoreWeave</t>
+  </si>
+  <si>
+    <t>AI算力</t>
+  </si>
+  <si>
+    <t>SMCI US</t>
+  </si>
+  <si>
+    <t>超微电脑</t>
+  </si>
+  <si>
+    <t>ETN US</t>
+  </si>
+  <si>
+    <t>伊顿</t>
   </si>
   <si>
     <t>Specialty Industrial Machinery</t>
   </si>
   <si>
-    <t>MMM US</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>Conglomerates</t>
-  </si>
-  <si>
-    <t>CRWD US</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>NEM US</t>
-  </si>
-  <si>
-    <t>纽曼矿业</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>ONDS US</t>
-  </si>
-  <si>
-    <t>Ondas</t>
-  </si>
-  <si>
-    <t>BMNR US</t>
-  </si>
-  <si>
-    <t>Bitmine Immersion Technologies</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>BKNG US</t>
-  </si>
-  <si>
-    <t>Booking Holdings</t>
-  </si>
-  <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
     <t>港股</t>
   </si>
   <si>
-    <t>1788 HK</t>
-  </si>
-  <si>
-    <t>国泰君安国际</t>
+    <t>20 HK</t>
+  </si>
+  <si>
+    <t>商汤-W</t>
+  </si>
+  <si>
+    <t>2099 HK</t>
+  </si>
+  <si>
+    <t>中国黄金国际</t>
+  </si>
+  <si>
+    <t>Other Precious Metals &amp; Mining</t>
   </si>
   <si>
     <t>2359 HK</t>
@@ -208,22 +211,13 @@
     <t>联想集团</t>
   </si>
   <si>
-    <t>Computer Hardware</t>
-  </si>
-  <si>
-    <t>669 HK</t>
-  </si>
-  <si>
-    <t>创科实业</t>
-  </si>
-  <si>
-    <t>Tools &amp; Accessories</t>
-  </si>
-  <si>
-    <t>100 HK</t>
-  </si>
-  <si>
-    <t>MINIMAX-W</t>
+    <t>322 HK</t>
+  </si>
+  <si>
+    <t>康师傅控股</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
   </si>
 </sst>
 </file>
@@ -617,10 +611,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="F2">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -629,7 +623,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.21210000000000001</v>
+        <v>0.29820000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -646,10 +640,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="F3">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -658,7 +652,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.19189999999999999</v>
+        <v>0.19439999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -675,10 +669,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F4">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -687,7 +681,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.2374</v>
+        <v>0.26900000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -704,10 +698,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="F5">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -716,7 +710,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.42130000000000001</v>
+        <v>0.2208</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -730,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -745,7 +739,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1971</v>
+        <v>0.27379999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -753,19 +747,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="F7">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -774,7 +768,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.3155</v>
+        <v>0.20519999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -782,19 +776,19 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
       <c r="E8">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="F8">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -803,7 +797,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.1734</v>
+        <v>0.27789999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -811,13 +805,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
       </c>
       <c r="E9">
         <v>0.85</v>
@@ -832,7 +826,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>5.3999999999999999E-2</v>
+        <v>0.14649999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -840,19 +834,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
       <c r="E10">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="F10">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -861,7 +855,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>4.9299999999999997E-2</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -869,19 +863,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E11">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="F11">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -890,7 +884,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.1981</v>
+        <v>0.30299999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -898,19 +892,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="F12">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -919,7 +913,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.12640000000000001</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -927,19 +921,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13">
-        <v>0.52</v>
+        <v>0.71</v>
       </c>
       <c r="F13">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -948,7 +942,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.2432</v>
+        <v>0.26719999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -956,13 +950,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>0.68</v>
@@ -977,7 +971,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.24909999999999999</v>
+        <v>0.25430000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -985,13 +979,13 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
       </c>
       <c r="E15">
         <v>0.85</v>
@@ -1006,28 +1000,28 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.1037</v>
+        <v>0.12790000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>51</v>
       </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E16">
+        <v>0.8</v>
+      </c>
+      <c r="F16">
         <v>0.7</v>
       </c>
-      <c r="F16">
-        <v>0.6</v>
-      </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
@@ -1035,27 +1029,27 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>7.3200000000000001E-2</v>
+        <v>0.1913</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
         <v>54</v>
       </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
-      </c>
       <c r="E17">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="F17">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1064,27 +1058,27 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.14430000000000001</v>
+        <v>0.17910000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
         <v>57</v>
       </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
-      </c>
       <c r="E18">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="F18">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1093,27 +1087,27 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.1857</v>
+        <v>0.14940000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
         <v>60</v>
       </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
       <c r="E19">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="F19">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1122,27 +1116,27 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.19320000000000001</v>
+        <v>0.19309999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F20">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1151,27 +1145,27 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>9.5200000000000007E-2</v>
+        <v>0.20169999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="F21">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1180,7 +1174,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.1757</v>
+        <v>4.5699999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A003676E-6F26-442F-B2BA-DEA06B9117FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804A5E2B-6CA6-465F-8A59-2847E032CE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>区域</t>
   </si>
@@ -65,6 +65,87 @@
     <t>美股</t>
   </si>
   <si>
+    <t>VLO US</t>
+  </si>
+  <si>
+    <t>瓦莱罗能源</t>
+  </si>
+  <si>
+    <t>油气炼化与销售</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>AMD US</t>
+  </si>
+  <si>
+    <t>超微半导体</t>
+  </si>
+  <si>
+    <t>AI芯片</t>
+  </si>
+  <si>
+    <t>CRWD US</t>
+  </si>
+  <si>
+    <t>CrowdStrike</t>
+  </si>
+  <si>
+    <t>基础软件</t>
+  </si>
+  <si>
+    <t>FTNT US</t>
+  </si>
+  <si>
+    <t>飞塔信息</t>
+  </si>
+  <si>
+    <t>BE US</t>
+  </si>
+  <si>
+    <t>Bloom Energy</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>COIN US</t>
+  </si>
+  <si>
+    <t>Coinbase</t>
+  </si>
+  <si>
+    <t>加密</t>
+  </si>
+  <si>
+    <t>MSTR US</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>应用软件</t>
+  </si>
+  <si>
+    <t>INTC US</t>
+  </si>
+  <si>
+    <t>英特尔</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
+    <t>CRCL US</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>资本市场</t>
+  </si>
+  <si>
     <t>DELL US</t>
   </si>
   <si>
@@ -74,16 +155,22 @@
     <t>计算机硬件</t>
   </si>
   <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
-    <t>VLO US</t>
-  </si>
-  <si>
-    <t>瓦莱罗能源</t>
-  </si>
-  <si>
-    <t>油气炼化与销售</t>
+    <t>DE US</t>
+  </si>
+  <si>
+    <t>迪尔股份</t>
+  </si>
+  <si>
+    <t>农业与工程机械</t>
+  </si>
+  <si>
+    <t>HOOD US</t>
+  </si>
+  <si>
+    <t>罗宾汉</t>
+  </si>
+  <si>
+    <t>券商/加密</t>
   </si>
   <si>
     <t>HPE US</t>
@@ -95,124 +182,46 @@
     <t>通信设备</t>
   </si>
   <si>
-    <t>BMNR US</t>
-  </si>
-  <si>
-    <t>Bitmine Immersion Technologies</t>
-  </si>
-  <si>
-    <t>资本市场</t>
-  </si>
-  <si>
-    <t>BE US</t>
-  </si>
-  <si>
-    <t>Bloom Energy</t>
-  </si>
-  <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>SNDK US</t>
-  </si>
-  <si>
-    <t>闪迪</t>
-  </si>
-  <si>
-    <t>CRCL US</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>MSTR US</t>
-  </si>
-  <si>
-    <t>Strategy</t>
-  </si>
-  <si>
-    <t>应用软件</t>
-  </si>
-  <si>
-    <t>COIN US</t>
-  </si>
-  <si>
-    <t>Coinbase</t>
-  </si>
-  <si>
-    <t>加密</t>
-  </si>
-  <si>
-    <t>RBLX US</t>
-  </si>
-  <si>
-    <t>罗布乐思</t>
-  </si>
-  <si>
-    <t>电子游戏与多媒体</t>
-  </si>
-  <si>
-    <t>HOOD US</t>
-  </si>
-  <si>
-    <t>罗宾汉</t>
-  </si>
-  <si>
-    <t>券商/加密</t>
-  </si>
-  <si>
-    <t>CRM US</t>
-  </si>
-  <si>
-    <t>赛富时</t>
-  </si>
-  <si>
-    <t>DVN US</t>
-  </si>
-  <si>
-    <t>戴文能源</t>
-  </si>
-  <si>
-    <t>油气勘探与生产</t>
+    <t>LITE US</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
   </si>
   <si>
     <t>港股</t>
   </si>
   <si>
-    <t>3939 HK</t>
-  </si>
-  <si>
-    <t>万国黄金集团</t>
-  </si>
-  <si>
-    <t>黄金</t>
-  </si>
-  <si>
-    <t>2099 HK</t>
-  </si>
-  <si>
-    <t>中国黄金国际</t>
-  </si>
-  <si>
-    <t>贵金属与采矿</t>
-  </si>
-  <si>
-    <t>1797 HK</t>
-  </si>
-  <si>
-    <t>东方甄选</t>
-  </si>
-  <si>
-    <t>Education &amp; Training Services</t>
-  </si>
-  <si>
-    <t>3696 HK</t>
-  </si>
-  <si>
-    <t>英矽智能</t>
-  </si>
-  <si>
-    <t>基础软件</t>
+    <t>1138 HK</t>
+  </si>
+  <si>
+    <t>中远海能</t>
+  </si>
+  <si>
+    <t>油气中游</t>
+  </si>
+  <si>
+    <t>992 HK</t>
+  </si>
+  <si>
+    <t>联想集团</t>
+  </si>
+  <si>
+    <t>2228 HK</t>
+  </si>
+  <si>
+    <t>晶泰控股</t>
+  </si>
+  <si>
+    <t>Health Information Services</t>
+  </si>
+  <si>
+    <t>1860 HK</t>
+  </si>
+  <si>
+    <t>汇量科技</t>
+  </si>
+  <si>
+    <t>Advertising Agencies</t>
   </si>
   <si>
     <t>6869 HK</t>
@@ -231,12 +240,6 @@
   </si>
   <si>
     <t>电子元件</t>
-  </si>
-  <si>
-    <t>2259 HK</t>
-  </si>
-  <si>
-    <t>紫金黄金国际</t>
   </si>
 </sst>
 </file>
@@ -587,8 +590,7 @@
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.15">
@@ -634,10 +636,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="F2">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -646,15 +648,15 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.19259999999999999</v>
+        <v>0.20280000000000001</v>
       </c>
       <c r="L2">
         <f>E2*100</f>
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="M2">
         <f>F2*100</f>
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.15">
@@ -671,10 +673,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -683,15 +685,15 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.1416</v>
+        <v>0.18410000000000001</v>
       </c>
       <c r="L3">
         <f>E3*100</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M3">
         <f>F3*100</f>
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
@@ -708,10 +710,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="F4">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -720,15 +722,15 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.18210000000000001</v>
+        <v>0.1807</v>
       </c>
       <c r="L4">
         <f>E4*100</f>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M4">
         <f>F4*100</f>
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.15">
@@ -742,13 +744,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="F5">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -757,15 +759,15 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.25230000000000002</v>
+        <v>0.18029999999999999</v>
       </c>
       <c r="L5">
         <f>E5*100</f>
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M5">
         <f>F5*100</f>
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
@@ -773,19 +775,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
       <c r="E6">
-        <v>0.66</v>
+        <v>0.69</v>
       </c>
       <c r="F6">
-        <v>0.56000000000000005</v>
+        <v>0.59</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -794,15 +796,15 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.24940000000000001</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="L6">
         <f>E6*100</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M6">
         <f>F6*100</f>
-        <v>56.000000000000007</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
@@ -810,19 +812,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
       <c r="E7">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F7">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -831,15 +833,15 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.24360000000000001</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="L7">
         <f>E7*100</f>
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M7">
         <f>F7*100</f>
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
@@ -853,13 +855,13 @@
         <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="F8">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -868,15 +870,15 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.2601</v>
+        <v>0.26290000000000002</v>
       </c>
       <c r="L8">
         <f>E8*100</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M8">
         <f>F8*100</f>
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.15">
@@ -884,13 +886,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>0.74</v>
@@ -905,7 +907,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.25969999999999999</v>
+        <v>0.189</v>
       </c>
       <c r="L9">
         <f>E9*100</f>
@@ -921,19 +923,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="F10">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -946,11 +948,11 @@
       </c>
       <c r="L10">
         <f>E10*100</f>
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M10">
         <f>F10*100</f>
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
@@ -958,13 +960,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>0.72</v>
@@ -979,7 +981,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.18809999999999999</v>
+        <v>0.19059999999999999</v>
       </c>
       <c r="L11">
         <f>E11*100</f>
@@ -995,20 +997,20 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
+        <v>0.85</v>
+      </c>
+      <c r="F12">
         <v>0.75</v>
       </c>
-      <c r="F12">
-        <v>0.65</v>
-      </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
@@ -1016,15 +1018,15 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.2019</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="L12">
         <f>E12*100</f>
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M12">
         <f>F12*100</f>
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.15">
@@ -1032,19 +1034,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E13">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="F13">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -1053,15 +1055,15 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.1454</v>
+        <v>0.19439999999999999</v>
       </c>
       <c r="L13">
         <f>E13*100</f>
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="M13">
         <f>F13*100</f>
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.15">
@@ -1069,19 +1071,19 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="F14">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -1090,35 +1092,35 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>9.7100000000000006E-2</v>
+        <v>0.1734</v>
       </c>
       <c r="L14">
         <f>E14*100</f>
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="M14">
         <f>F14*100</f>
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
         <v>48</v>
       </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
       <c r="E15">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
       <c r="F15">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1127,35 +1129,35 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>8.8400000000000006E-2</v>
+        <v>0.25469999999999998</v>
       </c>
       <c r="L15">
         <f>E15*100</f>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M15">
         <f>F15*100</f>
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F16">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1164,35 +1166,35 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.17760000000000001</v>
+        <v>0.16819999999999999</v>
       </c>
       <c r="L16">
         <f>E16*100</f>
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M16">
         <f>F16*100</f>
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E17">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F17">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1201,20 +1203,20 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.17699999999999999</v>
+        <v>0.2024</v>
       </c>
       <c r="L17">
         <f>E17*100</f>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M17">
         <f>F17*100</f>
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
@@ -1226,10 +1228,10 @@
         <v>59</v>
       </c>
       <c r="E18">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="F18">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1238,20 +1240,20 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.15459999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="L18">
         <f>E18*100</f>
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="M18">
         <f>F18*100</f>
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
         <v>60</v>
@@ -1263,10 +1265,10 @@
         <v>62</v>
       </c>
       <c r="E19">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="F19">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1275,20 +1277,20 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.23799999999999999</v>
+        <v>0.1605</v>
       </c>
       <c r="L19">
         <f>E19*100</f>
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="M19">
         <f>F19*100</f>
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
         <v>63</v>
@@ -1300,10 +1302,10 @@
         <v>65</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="F20">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1312,20 +1314,20 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.22939999999999999</v>
       </c>
       <c r="L20">
         <f>E20*100</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M20">
         <f>F20*100</f>
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
         <v>66</v>
@@ -1334,13 +1336,13 @@
         <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E21">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1349,15 +1351,15 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.20419999999999999</v>
+        <v>9.3700000000000006E-2</v>
       </c>
       <c r="L21">
         <f>E21*100</f>
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="M21">
         <f>F21*100</f>
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBA1193-6675-46A3-BD8A-7E399390E074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F835AF-0F27-46C1-A068-EE9B99C59D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-340" yWindow="10690" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
   <si>
     <t>区域</t>
   </si>
@@ -65,6 +52,48 @@
     <t>美股</t>
   </si>
   <si>
+    <t>HPE US</t>
+  </si>
+  <si>
+    <t>慧与科技</t>
+  </si>
+  <si>
+    <t>通信设备</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>LITE US</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>CRWD US</t>
+  </si>
+  <si>
+    <t>CrowdStrike</t>
+  </si>
+  <si>
+    <t>基础软件</t>
+  </si>
+  <si>
+    <t>PANW US</t>
+  </si>
+  <si>
+    <t>Palo Alto Networks</t>
+  </si>
+  <si>
+    <t>ON US</t>
+  </si>
+  <si>
+    <t>安森美半导体</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
     <t>AMD US</t>
   </si>
   <si>
@@ -74,7 +103,25 @@
     <t>AI芯片</t>
   </si>
   <si>
-    <t>欧式敲入</t>
+    <t>FTNT US</t>
+  </si>
+  <si>
+    <t>飞塔信息</t>
+  </si>
+  <si>
+    <t>NET US</t>
+  </si>
+  <si>
+    <t>Cloudflare</t>
+  </si>
+  <si>
+    <t>TER US</t>
+  </si>
+  <si>
+    <t>泰瑞达</t>
+  </si>
+  <si>
+    <t>半导体设备与材料</t>
   </si>
   <si>
     <t>DDOG US</t>
@@ -86,24 +133,6 @@
     <t>应用软件</t>
   </si>
   <si>
-    <t>NET US</t>
-  </si>
-  <si>
-    <t>Cloudflare</t>
-  </si>
-  <si>
-    <t>基础软件</t>
-  </si>
-  <si>
-    <t>HPE US</t>
-  </si>
-  <si>
-    <t>慧与科技</t>
-  </si>
-  <si>
-    <t>通信设备</t>
-  </si>
-  <si>
     <t>DELL US</t>
   </si>
   <si>
@@ -113,76 +142,28 @@
     <t>计算机硬件</t>
   </si>
   <si>
-    <t>CRWD US</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>META US</t>
-  </si>
-  <si>
-    <t>Meta平台</t>
-  </si>
-  <si>
-    <t>广告/AI</t>
-  </si>
-  <si>
-    <t>ARM US</t>
-  </si>
-  <si>
-    <t>Arm</t>
-  </si>
-  <si>
-    <t>AI半导体IP</t>
-  </si>
-  <si>
-    <t>RBLX US</t>
-  </si>
-  <si>
-    <t>罗布乐思</t>
-  </si>
-  <si>
-    <t>电子游戏与多媒体</t>
-  </si>
-  <si>
-    <t>SMCI US</t>
-  </si>
-  <si>
-    <t>超微电脑</t>
-  </si>
-  <si>
-    <t>BE US</t>
-  </si>
-  <si>
-    <t>Bloom Energy</t>
-  </si>
-  <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>CLS US</t>
-  </si>
-  <si>
-    <t>天弘科技</t>
-  </si>
-  <si>
-    <t>电子元件</t>
-  </si>
-  <si>
-    <t>ALAB US</t>
-  </si>
-  <si>
-    <t>阿斯特拉实验室</t>
-  </si>
-  <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>SNDK US</t>
-  </si>
-  <si>
-    <t>闪迪</t>
+    <t>COHR US</t>
+  </si>
+  <si>
+    <t>Coherent</t>
+  </si>
+  <si>
+    <t>AI光通信</t>
+  </si>
+  <si>
+    <t>RKLB US</t>
+  </si>
+  <si>
+    <t>Rocket Lab</t>
+  </si>
+  <si>
+    <t>航空航天与国防</t>
+  </si>
+  <si>
+    <t>SNPS US</t>
+  </si>
+  <si>
+    <t>新思科技</t>
   </si>
   <si>
     <t>港股</t>
@@ -203,6 +184,12 @@
     <t>油气中游</t>
   </si>
   <si>
+    <t>6809 HK</t>
+  </si>
+  <si>
+    <t>澜起科技</t>
+  </si>
+  <si>
     <t>1860 HK</t>
   </si>
   <si>
@@ -218,19 +205,13 @@
     <t>英矽智能</t>
   </si>
   <si>
-    <t>2269 HK</t>
-  </si>
-  <si>
-    <t>药明生物</t>
-  </si>
-  <si>
-    <t>生物科技</t>
-  </si>
-  <si>
-    <t>INTC US</t>
-  </si>
-  <si>
-    <t>英特尔</t>
+    <t>148 HK</t>
+  </si>
+  <si>
+    <t>建滔集团</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
   </si>
 </sst>
 </file>
@@ -624,10 +605,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="F2">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -636,7 +617,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.2</v>
+        <v>0.18110000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -650,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>0.75</v>
@@ -665,7 +646,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.1885</v>
+        <v>0.2571</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -673,19 +654,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
       <c r="E4">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="F4">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -694,7 +675,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.20960000000000001</v>
+        <v>0.1946</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -702,19 +683,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>0.73</v>
+        <v>0.81</v>
       </c>
       <c r="F5">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -723,7 +704,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.18110000000000001</v>
+        <v>0.19089999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -731,19 +712,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
       <c r="E6">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="F6">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -752,7 +733,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1943</v>
+        <v>0.21310000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -760,19 +741,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
       <c r="E7">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="F7">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -781,7 +762,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.187</v>
+        <v>0.19489999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -789,19 +770,19 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="F8">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -810,7 +791,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.13980000000000001</v>
+        <v>0.19270000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -818,19 +799,19 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="F9">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -839,7 +820,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.26650000000000001</v>
+        <v>0.2122</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -847,13 +828,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E10">
         <v>0.71</v>
@@ -868,7 +849,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.18279999999999999</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -876,19 +857,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="F11">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -897,7 +878,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.25519999999999998</v>
+        <v>0.20280000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -905,19 +886,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
       <c r="E12">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="F12">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -926,7 +907,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.2636</v>
+        <v>0.19539999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -934,19 +915,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
       </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
       <c r="E13">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="F13">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -955,7 +936,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.2059</v>
+        <v>0.26519999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -963,19 +944,19 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
       <c r="E14">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="F14">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -984,7 +965,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.25530000000000003</v>
+        <v>0.26550000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -992,19 +973,19 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="F15">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1013,27 +994,27 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.25290000000000001</v>
+        <v>0.1439</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F16">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1042,21 +1023,21 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.19800000000000001</v>
+        <v>0.19520000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
         <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
       </c>
       <c r="E17">
         <v>0.77</v>
@@ -1071,27 +1052,27 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.18490000000000001</v>
+        <v>0.19739999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E18">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="F18">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1100,27 +1081,27 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.1694</v>
+        <v>0.13450000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="E19">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="F19">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1129,27 +1110,27 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.1615</v>
+        <v>0.1628</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="E20">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="F20">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1158,27 +1139,27 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.20660000000000001</v>
+        <v>0.18340000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E21">
-        <v>0.71</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="F21">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1187,7 +1168,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.1774</v>
+        <v>2.93E-2</v>
       </c>
     </row>
   </sheetData>

--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F835AF-0F27-46C1-A068-EE9B99C59D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9421A670-3F63-49CD-9FC8-8913CEDB8A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -52,6 +65,33 @@
     <t>美股</t>
   </si>
   <si>
+    <t>PLTR US</t>
+  </si>
+  <si>
+    <t>帕兰提尔</t>
+  </si>
+  <si>
+    <t>AI软件</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>SNOW US</t>
+  </si>
+  <si>
+    <t>Snowflake</t>
+  </si>
+  <si>
+    <t>应用软件</t>
+  </si>
+  <si>
+    <t>DDOG US</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
     <t>HPE US</t>
   </si>
   <si>
@@ -61,118 +101,106 @@
     <t>通信设备</t>
   </si>
   <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
     <t>LITE US</t>
   </si>
   <si>
     <t>Lumentum</t>
   </si>
   <si>
+    <t>NET US</t>
+  </si>
+  <si>
+    <t>Cloudflare</t>
+  </si>
+  <si>
+    <t>基础软件</t>
+  </si>
+  <si>
+    <t>DELL US</t>
+  </si>
+  <si>
+    <t>戴尔科技</t>
+  </si>
+  <si>
+    <t>计算机硬件</t>
+  </si>
+  <si>
+    <t>PANW US</t>
+  </si>
+  <si>
+    <t>Palo Alto Networks</t>
+  </si>
+  <si>
+    <t>FTNT US</t>
+  </si>
+  <si>
+    <t>飞塔信息</t>
+  </si>
+  <si>
     <t>CRWD US</t>
   </si>
   <si>
     <t>CrowdStrike</t>
   </si>
   <si>
-    <t>基础软件</t>
-  </si>
-  <si>
-    <t>PANW US</t>
-  </si>
-  <si>
-    <t>Palo Alto Networks</t>
-  </si>
-  <si>
-    <t>ON US</t>
-  </si>
-  <si>
-    <t>安森美半导体</t>
-  </si>
-  <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>AMD US</t>
-  </si>
-  <si>
-    <t>超微半导体</t>
-  </si>
-  <si>
-    <t>AI芯片</t>
-  </si>
-  <si>
-    <t>FTNT US</t>
-  </si>
-  <si>
-    <t>飞塔信息</t>
-  </si>
-  <si>
-    <t>NET US</t>
-  </si>
-  <si>
-    <t>Cloudflare</t>
-  </si>
-  <si>
-    <t>TER US</t>
-  </si>
-  <si>
-    <t>泰瑞达</t>
-  </si>
-  <si>
-    <t>半导体设备与材料</t>
-  </si>
-  <si>
-    <t>DDOG US</t>
-  </si>
-  <si>
-    <t>Datadog</t>
-  </si>
-  <si>
-    <t>应用软件</t>
-  </si>
-  <si>
-    <t>DELL US</t>
-  </si>
-  <si>
-    <t>戴尔科技</t>
-  </si>
-  <si>
-    <t>计算机硬件</t>
-  </si>
-  <si>
-    <t>COHR US</t>
-  </si>
-  <si>
-    <t>Coherent</t>
-  </si>
-  <si>
-    <t>AI光通信</t>
-  </si>
-  <si>
-    <t>RKLB US</t>
-  </si>
-  <si>
-    <t>Rocket Lab</t>
-  </si>
-  <si>
-    <t>航空航天与国防</t>
-  </si>
-  <si>
-    <t>SNPS US</t>
-  </si>
-  <si>
-    <t>新思科技</t>
+    <t>ANET US</t>
+  </si>
+  <si>
+    <t>阿里斯塔</t>
+  </si>
+  <si>
+    <t>AI网络</t>
+  </si>
+  <si>
+    <t>SHOP US</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>CIEN US</t>
+  </si>
+  <si>
+    <t>Ciena</t>
+  </si>
+  <si>
+    <t>HIMS US</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers Health</t>
+  </si>
+  <si>
+    <t>专科与仿制药</t>
   </si>
   <si>
     <t>港股</t>
   </si>
   <si>
-    <t>992 HK</t>
-  </si>
-  <si>
-    <t>联想集团</t>
+    <t>2268 HK</t>
+  </si>
+  <si>
+    <t>药明合联</t>
+  </si>
+  <si>
+    <t>诊断与研究</t>
+  </si>
+  <si>
+    <t>1860 HK</t>
+  </si>
+  <si>
+    <t>汇量科技</t>
+  </si>
+  <si>
+    <t>Advertising Agencies</t>
+  </si>
+  <si>
+    <t>9926 HK</t>
+  </si>
+  <si>
+    <t>康方生物</t>
+  </si>
+  <si>
+    <t>生物科技</t>
   </si>
   <si>
     <t>1138 HK</t>
@@ -184,34 +212,19 @@
     <t>油气中游</t>
   </si>
   <si>
-    <t>6809 HK</t>
-  </si>
-  <si>
-    <t>澜起科技</t>
-  </si>
-  <si>
-    <t>1860 HK</t>
-  </si>
-  <si>
-    <t>汇量科技</t>
-  </si>
-  <si>
-    <t>Advertising Agencies</t>
-  </si>
-  <si>
-    <t>3696 HK</t>
-  </si>
-  <si>
-    <t>英矽智能</t>
-  </si>
-  <si>
-    <t>148 HK</t>
-  </si>
-  <si>
-    <t>建滔集团</t>
-  </si>
-  <si>
-    <t>Conglomerates</t>
+    <t>2359 HK</t>
+  </si>
+  <si>
+    <t>药明康德</t>
+  </si>
+  <si>
+    <t>772 HK</t>
+  </si>
+  <si>
+    <t>阅文集团</t>
+  </si>
+  <si>
+    <t>互联网内容与信息</t>
   </si>
 </sst>
 </file>
@@ -605,11 +618,11 @@
         <v>12</v>
       </c>
       <c r="E2">
+        <v>0.83</v>
+      </c>
+      <c r="F2">
         <v>0.73</v>
       </c>
-      <c r="F2">
-        <v>0.63</v>
-      </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
@@ -617,7 +630,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.18110000000000001</v>
+        <v>0.20080000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -631,13 +644,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F3">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -646,7 +659,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.2571</v>
+        <v>0.18279999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -654,19 +667,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
       <c r="E4">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F4">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -675,7 +688,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.1946</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -689,13 +702,13 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="F5">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -704,7 +717,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.19089999999999999</v>
+        <v>0.1691</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -712,19 +725,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
       <c r="E6">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="F6">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -733,7 +746,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.21310000000000001</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -750,10 +763,10 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="F7">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -762,7 +775,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.19489999999999999</v>
+        <v>0.21010000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -776,13 +789,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="F8">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -791,7 +804,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.19270000000000001</v>
+        <v>0.19769999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -799,19 +812,19 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="F9">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -820,7 +833,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.2122</v>
+        <v>0.1855</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -828,19 +841,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="F10">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -849,7 +862,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.2029</v>
+        <v>0.18690000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -863,13 +876,13 @@
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="F11">
-        <v>0.66</v>
+        <v>0.69</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -878,7 +891,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.20280000000000001</v>
+        <v>0.18709999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -886,20 +899,20 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>38</v>
       </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
       <c r="E12">
+        <v>0.84</v>
+      </c>
+      <c r="F12">
         <v>0.74</v>
       </c>
-      <c r="F12">
-        <v>0.64</v>
-      </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
@@ -907,7 +920,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.19539999999999999</v>
+        <v>0.1903</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -915,19 +928,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="F13">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -936,7 +949,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.26519999999999999</v>
+        <v>0.19980000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -944,19 +957,19 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F14">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -965,7 +978,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.26550000000000001</v>
+        <v>0.24329999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -973,19 +986,19 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E15">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="F15">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -994,27 +1007,27 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.1439</v>
+        <v>0.25459999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
       <c r="E16">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="F16">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1023,27 +1036,27 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.19520000000000001</v>
+        <v>0.14760000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
         <v>51</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
       <c r="E17">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F17">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1052,27 +1065,27 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.19739999999999999</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
         <v>54</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>55</v>
       </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
       <c r="E18">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="F18">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1081,12 +1094,12 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.13450000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
         <v>56</v>
@@ -1098,10 +1111,10 @@
         <v>58</v>
       </c>
       <c r="E19">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="F19">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1110,12 +1123,12 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.1628</v>
+        <v>0.2009</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
@@ -1124,13 +1137,13 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E20">
-        <v>0.64</v>
+        <v>0.81</v>
       </c>
       <c r="F20">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1139,12 +1152,12 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.18340000000000001</v>
+        <v>0.15540000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
         <v>61</v>
@@ -1156,10 +1169,10 @@
         <v>63</v>
       </c>
       <c r="E21">
-        <v>0.56999999999999995</v>
+        <v>0.81</v>
       </c>
       <c r="F21">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1168,7 +1181,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>2.93E-2</v>
+        <v>0.11070000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9421A670-3F63-49CD-9FC8-8913CEDB8A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E808556C-5E84-4C3C-94AD-B969ADBDD383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>区域</t>
   </si>
@@ -65,25 +52,43 @@
     <t>美股</t>
   </si>
   <si>
-    <t>PLTR US</t>
-  </si>
-  <si>
-    <t>帕兰提尔</t>
-  </si>
-  <si>
-    <t>AI软件</t>
+    <t>SHOP US</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>应用软件</t>
   </si>
   <si>
     <t>欧式敲入</t>
   </si>
   <si>
-    <t>SNOW US</t>
-  </si>
-  <si>
-    <t>Snowflake</t>
-  </si>
-  <si>
-    <t>应用软件</t>
+    <t>RCL US</t>
+  </si>
+  <si>
+    <t>皇家加勒比邮轮</t>
+  </si>
+  <si>
+    <t>旅游服务</t>
+  </si>
+  <si>
+    <t>MCK US</t>
+  </si>
+  <si>
+    <t>麦克森</t>
+  </si>
+  <si>
+    <t>Medical Distribution</t>
+  </si>
+  <si>
+    <t>SNPS US</t>
+  </si>
+  <si>
+    <t>新思科技</t>
+  </si>
+  <si>
+    <t>基础软件</t>
   </si>
   <si>
     <t>DDOG US</t>
@@ -92,130 +97,88 @@
     <t>Datadog</t>
   </si>
   <si>
-    <t>HPE US</t>
-  </si>
-  <si>
-    <t>慧与科技</t>
-  </si>
-  <si>
-    <t>通信设备</t>
-  </si>
-  <si>
-    <t>LITE US</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>NET US</t>
-  </si>
-  <si>
-    <t>Cloudflare</t>
-  </si>
-  <si>
-    <t>基础软件</t>
-  </si>
-  <si>
-    <t>DELL US</t>
-  </si>
-  <si>
-    <t>戴尔科技</t>
-  </si>
-  <si>
-    <t>计算机硬件</t>
-  </si>
-  <si>
-    <t>PANW US</t>
-  </si>
-  <si>
-    <t>Palo Alto Networks</t>
-  </si>
-  <si>
-    <t>FTNT US</t>
-  </si>
-  <si>
-    <t>飞塔信息</t>
-  </si>
-  <si>
-    <t>CRWD US</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>ANET US</t>
-  </si>
-  <si>
-    <t>阿里斯塔</t>
-  </si>
-  <si>
-    <t>AI网络</t>
-  </si>
-  <si>
-    <t>SHOP US</t>
-  </si>
-  <si>
-    <t>Shopify</t>
-  </si>
-  <si>
-    <t>CIEN US</t>
-  </si>
-  <si>
-    <t>Ciena</t>
-  </si>
-  <si>
-    <t>HIMS US</t>
-  </si>
-  <si>
-    <t>Hims &amp; Hers Health</t>
-  </si>
-  <si>
-    <t>专科与仿制药</t>
+    <t>COP US</t>
+  </si>
+  <si>
+    <t>康菲石油</t>
+  </si>
+  <si>
+    <t>油气勘探与生产</t>
+  </si>
+  <si>
+    <t>CCL US</t>
+  </si>
+  <si>
+    <t>嘉年华邮轮</t>
+  </si>
+  <si>
+    <t>ACN US</t>
+  </si>
+  <si>
+    <t>埃森哲</t>
+  </si>
+  <si>
+    <t>IT服务</t>
+  </si>
+  <si>
+    <t>CRWV US</t>
+  </si>
+  <si>
+    <t>CoreWeave</t>
+  </si>
+  <si>
+    <t>AI算力</t>
+  </si>
+  <si>
+    <t>PYPL US</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>信贷服务</t>
+  </si>
+  <si>
+    <t>CDNS US</t>
+  </si>
+  <si>
+    <t>铿腾电子</t>
+  </si>
+  <si>
+    <t>AMGN US</t>
+  </si>
+  <si>
+    <t>安进</t>
+  </si>
+  <si>
+    <t>制药</t>
+  </si>
+  <si>
+    <t>XOM US</t>
+  </si>
+  <si>
+    <t>埃克森美孚</t>
+  </si>
+  <si>
+    <t>综合油气</t>
+  </si>
+  <si>
+    <t>MSFT US</t>
+  </si>
+  <si>
+    <t>微软</t>
+  </si>
+  <si>
+    <t>云/AI</t>
   </si>
   <si>
     <t>港股</t>
   </si>
   <si>
-    <t>2268 HK</t>
-  </si>
-  <si>
-    <t>药明合联</t>
-  </si>
-  <si>
-    <t>诊断与研究</t>
-  </si>
-  <si>
-    <t>1860 HK</t>
-  </si>
-  <si>
-    <t>汇量科技</t>
-  </si>
-  <si>
-    <t>Advertising Agencies</t>
-  </si>
-  <si>
-    <t>9926 HK</t>
-  </si>
-  <si>
-    <t>康方生物</t>
-  </si>
-  <si>
-    <t>生物科技</t>
-  </si>
-  <si>
-    <t>1138 HK</t>
-  </si>
-  <si>
-    <t>中远海能</t>
-  </si>
-  <si>
-    <t>油气中游</t>
-  </si>
-  <si>
-    <t>2359 HK</t>
-  </si>
-  <si>
-    <t>药明康德</t>
+    <t>268 HK</t>
+  </si>
+  <si>
+    <t>金蝶国际</t>
   </si>
   <si>
     <t>772 HK</t>
@@ -225,6 +188,33 @@
   </si>
   <si>
     <t>互联网内容与信息</t>
+  </si>
+  <si>
+    <t>LLY US</t>
+  </si>
+  <si>
+    <t>礼来</t>
+  </si>
+  <si>
+    <t>1797 HK</t>
+  </si>
+  <si>
+    <t>东方甄选</t>
+  </si>
+  <si>
+    <t>Education &amp; Training Services</t>
+  </si>
+  <si>
+    <t>6651 HK</t>
+  </si>
+  <si>
+    <t>五一视界</t>
+  </si>
+  <si>
+    <t>9901 HK</t>
+  </si>
+  <si>
+    <t>新东方-S</t>
   </si>
 </sst>
 </file>
@@ -618,10 +608,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="F2">
-        <v>0.73</v>
+        <v>0.69</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -630,7 +620,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.20080000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -647,10 +637,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -659,7 +649,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.18279999999999999</v>
+        <v>0.15770000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -673,13 +663,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="F4">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -688,7 +678,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.2014</v>
+        <v>6.2100000000000002E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -696,19 +686,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="F5">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -717,7 +707,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.1691</v>
+        <v>0.1394</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -725,19 +715,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F6">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -746,7 +736,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.2457</v>
+        <v>0.20449999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -754,19 +744,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="F7">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -775,7 +765,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.21010000000000001</v>
+        <v>7.22E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -783,19 +773,19 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="F8">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -804,7 +794,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.19769999999999999</v>
+        <v>0.13739999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -818,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="F9">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -833,7 +823,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.1855</v>
+        <v>0.13039999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -841,19 +831,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E10">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="F10">
-        <v>0.72</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -862,7 +852,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.18690000000000001</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -870,19 +860,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E11">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="F11">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -891,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.18709999999999999</v>
+        <v>9.7600000000000006E-2</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -899,13 +889,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <v>0.84</v>
@@ -920,7 +910,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.1903</v>
+        <v>0.13789999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -928,19 +918,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E13">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="F13">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -949,7 +939,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.19980000000000001</v>
+        <v>7.7399999999999997E-2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -957,19 +947,19 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E14">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="F14">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -978,7 +968,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.24329999999999999</v>
+        <v>6.2100000000000002E-2</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -986,19 +976,19 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E15">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="F15">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1007,27 +997,27 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.25459999999999999</v>
+        <v>6.83E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="F16">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1036,28 +1026,28 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.14760000000000001</v>
+        <v>0.20469999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E17">
+        <v>0.81</v>
+      </c>
+      <c r="F17">
         <v>0.71</v>
       </c>
-      <c r="F17">
-        <v>0.61</v>
-      </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
@@ -1065,27 +1055,27 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.1701</v>
+        <v>0.11219999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E18">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="F18">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1094,27 +1084,27 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.19800000000000001</v>
+        <v>9.9199999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="F19">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1123,27 +1113,27 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.2009</v>
+        <v>0.16370000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>0.81</v>
+        <v>0.65</v>
       </c>
       <c r="F20">
-        <v>0.71</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1152,27 +1142,27 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.15540000000000001</v>
+        <v>9.2600000000000002E-2</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E21">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="F21">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1181,7 +1171,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.11070000000000001</v>
+        <v>0.13320000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E808556C-5E84-4C3C-94AD-B969ADBDD383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360FFB91-3D77-4CFF-8EE2-D8D9F96AE2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,6 +52,27 @@
     <t>美股</t>
   </si>
   <si>
+    <t>COP US</t>
+  </si>
+  <si>
+    <t>康菲石油</t>
+  </si>
+  <si>
+    <t>油气勘探与生产</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>ELV US</t>
+  </si>
+  <si>
+    <t>Elevance Health</t>
+  </si>
+  <si>
+    <t>医疗保险</t>
+  </si>
+  <si>
     <t>SHOP US</t>
   </si>
   <si>
@@ -61,16 +82,34 @@
     <t>应用软件</t>
   </si>
   <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
-    <t>RCL US</t>
-  </si>
-  <si>
-    <t>皇家加勒比邮轮</t>
-  </si>
-  <si>
-    <t>旅游服务</t>
+    <t>ADP US</t>
+  </si>
+  <si>
+    <t>自动数据处理</t>
+  </si>
+  <si>
+    <t>CVX US</t>
+  </si>
+  <si>
+    <t>雪佛龙</t>
+  </si>
+  <si>
+    <t>综合油气</t>
+  </si>
+  <si>
+    <t>LNG US</t>
+  </si>
+  <si>
+    <t>切尼尔能源</t>
+  </si>
+  <si>
+    <t>油气中游</t>
+  </si>
+  <si>
+    <t>XOM US</t>
+  </si>
+  <si>
+    <t>埃克森美孚</t>
   </si>
   <si>
     <t>MCK US</t>
@@ -82,34 +121,40 @@
     <t>Medical Distribution</t>
   </si>
   <si>
-    <t>SNPS US</t>
-  </si>
-  <si>
-    <t>新思科技</t>
-  </si>
-  <si>
-    <t>基础软件</t>
-  </si>
-  <si>
-    <t>DDOG US</t>
-  </si>
-  <si>
-    <t>Datadog</t>
-  </si>
-  <si>
-    <t>COP US</t>
-  </si>
-  <si>
-    <t>康菲石油</t>
-  </si>
-  <si>
-    <t>油气勘探与生产</t>
-  </si>
-  <si>
-    <t>CCL US</t>
-  </si>
-  <si>
-    <t>嘉年华邮轮</t>
+    <t>OXY US</t>
+  </si>
+  <si>
+    <t>西方石油</t>
+  </si>
+  <si>
+    <t>SPOT US</t>
+  </si>
+  <si>
+    <t>声田</t>
+  </si>
+  <si>
+    <t>互联网内容与信息</t>
+  </si>
+  <si>
+    <t>DVN US</t>
+  </si>
+  <si>
+    <t>戴文能源</t>
+  </si>
+  <si>
+    <t>INTU US</t>
+  </si>
+  <si>
+    <t>财捷</t>
+  </si>
+  <si>
+    <t>NOW US</t>
+  </si>
+  <si>
+    <t>ServiceNow</t>
+  </si>
+  <si>
+    <t>AI软件</t>
   </si>
   <si>
     <t>ACN US</t>
@@ -121,79 +166,28 @@
     <t>IT服务</t>
   </si>
   <si>
-    <t>CRWV US</t>
-  </si>
-  <si>
-    <t>CoreWeave</t>
-  </si>
-  <si>
-    <t>AI算力</t>
-  </si>
-  <si>
-    <t>PYPL US</t>
-  </si>
-  <si>
-    <t>PayPal</t>
-  </si>
-  <si>
-    <t>信贷服务</t>
-  </si>
-  <si>
-    <t>CDNS US</t>
-  </si>
-  <si>
-    <t>铿腾电子</t>
-  </si>
-  <si>
-    <t>AMGN US</t>
-  </si>
-  <si>
-    <t>安进</t>
-  </si>
-  <si>
-    <t>制药</t>
-  </si>
-  <si>
-    <t>XOM US</t>
-  </si>
-  <si>
-    <t>埃克森美孚</t>
-  </si>
-  <si>
-    <t>综合油气</t>
-  </si>
-  <si>
-    <t>MSFT US</t>
-  </si>
-  <si>
-    <t>微软</t>
-  </si>
-  <si>
-    <t>云/AI</t>
-  </si>
-  <si>
     <t>港股</t>
   </si>
   <si>
+    <t>6651 HK</t>
+  </si>
+  <si>
+    <t>五一视界</t>
+  </si>
+  <si>
     <t>268 HK</t>
   </si>
   <si>
     <t>金蝶国际</t>
   </si>
   <si>
-    <t>772 HK</t>
-  </si>
-  <si>
-    <t>阅文集团</t>
-  </si>
-  <si>
-    <t>互联网内容与信息</t>
-  </si>
-  <si>
-    <t>LLY US</t>
-  </si>
-  <si>
-    <t>礼来</t>
+    <t>2715 HK</t>
+  </si>
+  <si>
+    <t>埃斯顿</t>
+  </si>
+  <si>
+    <t>通信设备</t>
   </si>
   <si>
     <t>1797 HK</t>
@@ -205,16 +199,22 @@
     <t>Education &amp; Training Services</t>
   </si>
   <si>
-    <t>6651 HK</t>
-  </si>
-  <si>
-    <t>五一视界</t>
-  </si>
-  <si>
-    <t>9901 HK</t>
-  </si>
-  <si>
-    <t>新东方-S</t>
+    <t>2525 HK</t>
+  </si>
+  <si>
+    <t>禾赛-W</t>
+  </si>
+  <si>
+    <t>汽车零部件</t>
+  </si>
+  <si>
+    <t>6693 HK</t>
+  </si>
+  <si>
+    <t>赤峰黄金</t>
+  </si>
+  <si>
+    <t>黄金</t>
   </si>
 </sst>
 </file>
@@ -257,9 +257,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="F2">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -620,7 +621,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.20499999999999999</v>
+        <v>8.2199999999999995E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -649,7 +650,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.15770000000000001</v>
+        <v>6.93E-2</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -666,10 +667,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="F4">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -678,7 +679,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>6.2100000000000002E-2</v>
+        <v>0.20630000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -692,13 +693,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="F5">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -707,7 +708,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.1394</v>
+        <v>6.1199999999999997E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -715,19 +716,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
       <c r="E6">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="F6">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -736,7 +737,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.20449999999999999</v>
+        <v>6.3200000000000006E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -765,7 +766,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>7.22E-2</v>
+        <v>7.4399999999999994E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -779,13 +780,13 @@
         <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="F8">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -794,7 +795,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.13739999999999999</v>
+        <v>6.9699999999999998E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -823,7 +824,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.13039999999999999</v>
+        <v>7.0699999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -837,13 +838,13 @@
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="F10">
-        <v>0.57999999999999996</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -852,7 +853,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.33</v>
+        <v>9.3600000000000003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -860,13 +861,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
       </c>
       <c r="E11">
         <v>0.85</v>
@@ -881,7 +882,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>9.7600000000000006E-2</v>
+        <v>0.12759999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -889,19 +890,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="F12">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -910,7 +911,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.13789999999999999</v>
+        <v>0.10929999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -918,19 +919,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="F13">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -939,7 +940,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>7.7399999999999997E-2</v>
+        <v>0.19769999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -947,19 +948,19 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
         <v>44</v>
       </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
       <c r="E14">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="F14">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -968,7 +969,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>6.2100000000000002E-2</v>
+        <v>0.2009</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -976,13 +977,13 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
         <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
       </c>
       <c r="E15">
         <v>0.85</v>
@@ -997,27 +998,27 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>6.83E-2</v>
+        <v>0.14580000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="F16">
-        <v>0.69</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1026,27 +1027,27 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.20469999999999999</v>
+        <v>9.1499999999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E17">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="F17">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1055,27 +1056,27 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.11219999999999999</v>
+        <v>0.19139999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18">
-        <v>0.85</v>
-      </c>
-      <c r="F18">
-        <v>0.75</v>
+        <v>55</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1084,27 +1085,27 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>9.9199999999999997E-2</v>
+        <v>0.1089</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
         <v>58</v>
       </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
       <c r="E19">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F19">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1113,28 +1114,28 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.16370000000000001</v>
+        <v>0.17979999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
         <v>61</v>
       </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
       <c r="E20">
+        <v>0.75</v>
+      </c>
+      <c r="F20">
         <v>0.65</v>
       </c>
-      <c r="F20">
-        <v>0.55000000000000004</v>
-      </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
@@ -1142,27 +1143,27 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>9.2600000000000002E-2</v>
+        <v>0.15679999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
         <v>63</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>64</v>
       </c>
-      <c r="D21" t="s">
-        <v>60</v>
-      </c>
       <c r="E21">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F21">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1171,7 +1172,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.13320000000000001</v>
+        <v>0.1857</v>
       </c>
     </row>
   </sheetData>
